--- a/research/traditional_assets/database/data/pakistan/pakistan_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_insurance_general.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.492</v>
+        <v>-0.355</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="I2">
-        <v>-0.1428571428571428</v>
+        <v>0.12</v>
       </c>
       <c r="J2">
-        <v>-0.1428571428571428</v>
+        <v>0.12</v>
       </c>
       <c r="K2">
-        <v>-0.003</v>
+        <v>0.003</v>
       </c>
       <c r="L2">
-        <v>-0.1428571428571428</v>
+        <v>0.12</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,25 +636,16 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.02857142857142857</v>
+        <v>-0.02857142857142857</v>
       </c>
       <c r="X2">
-        <v>0.08999844342096343</v>
+        <v>0.1541982539165212</v>
       </c>
       <c r="Y2">
-        <v>-0.06142701484953485</v>
-      </c>
-      <c r="Z2">
-        <v>-0.1981132075471698</v>
-      </c>
-      <c r="AA2">
-        <v>0.02830188679245283</v>
+        <v>-0.1827696824879498</v>
       </c>
       <c r="AB2">
-        <v>0.08999844342096343</v>
-      </c>
-      <c r="AC2">
-        <v>-0.0616965566285106</v>
+        <v>0.1541982539165212</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -685,12 +676,6 @@
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>-0</v>
-      </c>
-      <c r="AP2">
-        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -710,25 +695,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.492</v>
+        <v>-0.355</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="I3">
-        <v>-0.1428571428571428</v>
+        <v>0.12</v>
       </c>
       <c r="J3">
-        <v>-0.1428571428571428</v>
+        <v>0.12</v>
       </c>
       <c r="K3">
-        <v>-0.003</v>
+        <v>0.003</v>
       </c>
       <c r="L3">
-        <v>-0.1428571428571428</v>
+        <v>0.12</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,7 +722,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -746,7 +731,7 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,25 +743,16 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.02857142857142857</v>
+        <v>-0.02857142857142857</v>
       </c>
       <c r="X3">
-        <v>0.08999844342096343</v>
+        <v>0.1541982539165212</v>
       </c>
       <c r="Y3">
-        <v>-0.06142701484953485</v>
-      </c>
-      <c r="Z3">
-        <v>-0.1981132075471698</v>
-      </c>
-      <c r="AA3">
-        <v>0.02830188679245283</v>
+        <v>-0.1827696824879498</v>
       </c>
       <c r="AB3">
-        <v>0.08999844342096343</v>
-      </c>
-      <c r="AC3">
-        <v>-0.0616965566285106</v>
+        <v>0.1541982539165212</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -807,12 +783,6 @@
       </c>
       <c r="AM3">
         <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>-0</v>
-      </c>
-      <c r="AP3">
-        <v>-0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/pakistan/pakistan_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_insurance_general.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.355</v>
+        <v>0.302</v>
       </c>
       <c r="G2">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.12</v>
+        <v>0.681159420289855</v>
       </c>
       <c r="J2">
-        <v>0.12</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="K2">
-        <v>0.003</v>
+        <v>0.033</v>
       </c>
       <c r="L2">
-        <v>0.12</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,22 +630,22 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.008547008547008546</v>
       </c>
       <c r="W2">
-        <v>-0.02857142857142857</v>
+        <v>-0.3793103448275862</v>
       </c>
       <c r="X2">
-        <v>0.1541982539165212</v>
+        <v>0.1584895525582773</v>
       </c>
       <c r="Y2">
-        <v>-0.1827696824879498</v>
+        <v>-0.5377998973858635</v>
       </c>
       <c r="AB2">
-        <v>0.1541982539165212</v>
+        <v>0.1584895525582773</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -657,7 +657,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -666,10 +666,10 @@
         <v>-0</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>-0.008620689655172414</v>
       </c>
       <c r="AK2">
-        <v>-0</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -695,25 +695,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.355</v>
+        <v>0.302</v>
       </c>
       <c r="G3">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.12</v>
+        <v>0.681159420289855</v>
       </c>
       <c r="J3">
-        <v>0.12</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="K3">
-        <v>0.003</v>
+        <v>0.033</v>
       </c>
       <c r="L3">
-        <v>0.12</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,22 +737,22 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.008547008547008546</v>
       </c>
       <c r="W3">
-        <v>-0.02857142857142857</v>
+        <v>-0.3793103448275862</v>
       </c>
       <c r="X3">
-        <v>0.1541982539165212</v>
+        <v>0.1584895525582773</v>
       </c>
       <c r="Y3">
-        <v>-0.1827696824879498</v>
+        <v>-0.5377998973858635</v>
       </c>
       <c r="AB3">
-        <v>0.1541982539165212</v>
+        <v>0.1584895525582773</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -773,10 +773,10 @@
         <v>-0</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.008620689655172414</v>
       </c>
       <c r="AK3">
-        <v>-0</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="AL3">
         <v>0</v>
